--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingError.xlsx
@@ -918,10 +918,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1243,14 +1243,14 @@
     <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="17.375" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:10">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1278,39 +1278,39 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
